--- a/data/3.meta_data/basic_info/26_07_basic_info.xlsx
+++ b/data/3.meta_data/basic_info/26_07_basic_info.xlsx
@@ -661,6 +661,11 @@
           <t>Hopwood, Christopher J.</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Hopwood</t>
+        </is>
+      </c>
       <c r="K3">
         <v>2026</v>
       </c>
@@ -734,6 +739,11 @@
           <t>Allemand, Mathias and Olaru, Gabriel and Hill, Patrick L.</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Allemand et al.</t>
+        </is>
+      </c>
       <c r="K4">
         <v>2026</v>
       </c>
@@ -745,6 +755,11 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>include</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>changegoals; volitionalchange</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -851,6 +866,11 @@
           <t>Springstein, Tabea and Bankston, Anna C. and English, Tammy</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Springstein et al.</t>
+        </is>
+      </c>
       <c r="K5">
         <v>2026</v>
       </c>
@@ -966,6 +986,11 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>Feraco, Tommaso and Calderan, Margherita and Pellegrino, Gerardo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Feraco et al.</t>
         </is>
       </c>
       <c r="K6">
